--- a/example/i18n/langs/_todo_en.xlsx
+++ b/example/i18n/langs/_todo_en.xlsx
@@ -62,8 +62,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -207,22 +206,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>other.ArgCaptureMode</t>
+          <t>other.drop</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Snapshot</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t>name</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>快照模式</t>
+          <t>测试掉落</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -234,22 +233,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>other.ArgCaptureMode</t>
+          <t>other.drop</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dynamic</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t>name</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>动态模式</t>
+          <t>剧情任务测试2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -266,7 +265,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -276,7 +275,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>测试掉落</t>
+          <t>通告栏掉落染色模板1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -288,12 +287,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>other.drop</t>
+          <t>other.loot</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -303,7 +302,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>剧情任务测试2</t>
+          <t>测试掉落</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -315,12 +314,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>other.drop</t>
+          <t>other.loot</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -330,7 +329,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>通告栏掉落染色模板1</t>
+          <t>小宝箱</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -347,7 +346,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -357,7 +356,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>测试掉落</t>
+          <t>中宝箱</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -374,7 +373,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,7 +383,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>小宝箱</t>
+          <t>大宝箱</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -401,7 +400,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -411,7 +410,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>中宝箱</t>
+          <t>测试掉落2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -428,7 +427,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -438,7 +437,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>大宝箱</t>
+          <t>剧情任务测试1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -455,7 +454,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -465,7 +464,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>测试掉落2</t>
+          <t>剧情任务测试2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -482,7 +481,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -492,7 +491,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>剧情任务测试1</t>
+          <t>通告栏掉落染色模板1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -509,7 +508,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -519,7 +518,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>剧情任务测试2</t>
+          <t>通告栏掉落染色模板2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -536,7 +535,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -546,7 +545,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>通告栏掉落染色模板1</t>
+          <t>通告栏掉落染色模板3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -558,22 +557,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>other.loot</t>
+          <t>task.task</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name-0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>通告栏掉落染色模板2</t>
+          <t>和npc对话</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -585,22 +584,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>other.loot</t>
+          <t>task.task</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name-1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>通告栏掉落染色模板3</t>
+          <t>和npc对话</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -617,7 +616,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -627,7 +626,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>和npc对话</t>
+          <t>收集物品</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -644,7 +643,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -654,7 +653,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>和npc对话</t>
+          <t>收集物品</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -671,7 +670,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -681,7 +680,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>收集物品</t>
+          <t>杀怪并且收集物品</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -698,7 +697,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -708,7 +707,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>收集物品</t>
+          <t>杀怪并且收集物品</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -725,7 +724,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -735,7 +734,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>杀怪并且收集物品</t>
+          <t>杀怪对话并且收集物品</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -752,7 +751,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -762,7 +761,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>杀怪并且收集物品</t>
+          <t>杀怪对话并且收集物品</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -779,7 +778,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -789,7 +788,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>杀怪对话并且收集物品</t>
+          <t>聊天并且杀怪</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -806,7 +805,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -816,7 +815,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>杀怪对话并且收集物品</t>
+          <t>测试转义符号</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -833,7 +832,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -843,7 +842,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>聊天并且杀怪</t>
+          <t>测试</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -860,7 +859,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -870,7 +869,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>测试转义符号</t>
+          <t>测试无参数得bean</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -887,7 +886,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -897,7 +896,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>测试</t>
+          <t>测试2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -914,7 +913,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -924,7 +923,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>测试无参数得bean</t>
+          <t>测试默认bean</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -936,12 +935,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>task.task</t>
+          <t>task.task2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -951,7 +950,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>测试2</t>
+          <t>测试用</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -963,22 +962,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>task.task</t>
+          <t>task.task2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>name-1</t>
+          <t>name-0</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>测试默认bean</t>
+          <t>和npc对话</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -995,17 +994,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>name-0</t>
+          <t>name-1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>测试用</t>
+          <t>和npc对话</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1022,7 +1021,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1032,7 +1031,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>和npc对话</t>
+          <t>收集物品</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1049,7 +1048,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1059,7 +1058,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>和npc对话</t>
+          <t>收集物品</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1076,7 +1075,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1086,7 +1085,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>收集物品</t>
+          <t>杀怪并且收集物品</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1103,7 +1102,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1113,7 +1112,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>收集物品</t>
+          <t>杀怪并且收集物品</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1130,7 +1129,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1140,7 +1139,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>杀怪并且收集物品</t>
+          <t>杀怪对话并且收集物品</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1157,7 +1156,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1167,7 +1166,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>杀怪并且收集物品</t>
+          <t>杀怪对话并且收集物品</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1184,7 +1183,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1194,7 +1193,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>杀怪对话并且收集物品</t>
+          <t>聊天并且杀怪</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1211,7 +1210,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1221,7 +1220,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>杀怪对话并且收集物品</t>
+          <t>测试转义符号</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1238,7 +1237,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1248,7 +1247,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>聊天并且杀怪</t>
+          <t>测试</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1265,7 +1264,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1275,7 +1274,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>测试转义符号</t>
+          <t>测试无参数得bean</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1292,7 +1291,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1302,7 +1301,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>测试</t>
+          <t>测试2</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1319,7 +1318,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1329,64 +1328,10 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>测试无参数得bean</t>
+          <t>测试默认bean</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>task.task2</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>name-0</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>测试2</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>task.task2</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>name-1</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>测试默认bean</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/example/i18n/langs/_todo_en.xlsx
+++ b/example/i18n/langs/_todo_en.xlsx
@@ -98,7 +98,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>equip.jewelrysuit</t>
+          <t>equip.jewelry_suit</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -125,7 +125,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>equip.jewelrysuit</t>
+          <t>equip.jewelry_suit</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -152,7 +152,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>equip.jewelrysuit</t>
+          <t>equip.jewelry_suit</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -179,7 +179,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>equip.jewelrysuit</t>
+          <t>equip.jewelry_suit</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1391,7 +1391,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>equip.jewelrysuit</t>
+          <t>equip.jewelry_suit</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1418,7 +1418,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>equip.jewelrysuit</t>
+          <t>equip.jewelry_suit</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1445,7 +1445,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>equip.jewelrysuit</t>
+          <t>equip.jewelry_suit</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
